--- a/Configs/GameConfig/Datas/buff.xlsx
+++ b/Configs/GameConfig/Datas/buff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra71f9f545c594c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b65d97f1f8441a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -343,7 +343,7 @@
         <x:v>##var</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>type</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="C1" t="str">
         <x:v>name</x:v>
@@ -414,7 +414,7 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>类型(主键)</x:v>
+        <x:v>ID(主键)</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>名称</x:v>
@@ -441,7 +441,7 @@
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="str">
         <x:v>attPower</x:v>
@@ -464,7 +464,7 @@
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>attSpeed</x:v>
@@ -487,7 +487,7 @@
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" t="str">
         <x:v>attRange</x:v>
@@ -510,7 +510,7 @@
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>moveSpeed</x:v>
@@ -533,7 +533,7 @@
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>maxHp</x:v>
@@ -556,7 +556,7 @@
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" t="str">
         <x:v>hp</x:v>
@@ -579,7 +579,7 @@
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>scale</x:v>
@@ -602,7 +602,7 @@
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" t="str">
         <x:v>custom</x:v>
@@ -623,7 +623,7 @@
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" t="str">
         <x:v>stun</x:v>
@@ -648,7 +648,7 @@
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" t="str">
         <x:v>fall</x:v>
@@ -673,7 +673,7 @@
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" t="str">
         <x:v>pierce</x:v>
@@ -698,7 +698,7 @@
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C16" t="str">
         <x:v>electrocute</x:v>
@@ -723,7 +723,7 @@
     <x:row r="17">
       <x:c r="A17"/>
       <x:c r="B17" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" t="str">
         <x:v>knockback</x:v>
@@ -748,7 +748,7 @@
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" t="str">
         <x:v>chaos</x:v>
@@ -773,7 +773,7 @@
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C19" t="str">
         <x:v>burnStatic</x:v>
@@ -798,7 +798,7 @@
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" t="str">
         <x:v>limit</x:v>
@@ -821,7 +821,7 @@
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" t="str">
         <x:v>lock</x:v>
@@ -846,7 +846,7 @@
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" t="str">
         <x:v>knockdown</x:v>
@@ -871,7 +871,7 @@
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" t="str">
         <x:v>suppression</x:v>
@@ -896,7 +896,7 @@
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" t="str">
         <x:v>charm</x:v>

--- a/Configs/GameConfig/Datas/buff.xlsx
+++ b/Configs/GameConfig/Datas/buff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b65d97f1f8441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reee1b6bbc1f94b1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -414,28 +414,28 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
+        <x:v>全局唯一 Buff 数字 ID</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>名称</x:v>
+        <x:v>稳定英文键</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>中文标签</x:v>
+        <x:v>中文显示名，可空</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>类别</x:v>
+        <x:v>类别：0=Numeric 数值型 / 1=State 状态型 / 2=Custom 自定义处理器</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>通道列表</x:v>
+        <x:v>通道列表。Numeric：0攻击/1攻速/2范围/3移速/4最大生命/5当前生命/6缩放；State：0禁移动/1禁攻击/2改变选敌/3压制/4伤害脉冲/5击退脉冲/6移动锁定</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>叠层策略</x:v>
+        <x:v>叠层策略，严格填 Add / Refresh / Replace</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>最大层数</x:v>
+        <x:v>最大层数，必须大于 0</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>冲突键</x:v>
+        <x:v>冲突键，同键的其他 Buff 会被替换；无互斥需求留空</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
